--- a/CORTES DE CAJA/2026/7)JULIO/LISTA DE LAS VENTAS SEMANA 25 DE JULIO -26.xlsx
+++ b/CORTES DE CAJA/2026/7)JULIO/LISTA DE LAS VENTAS SEMANA 25 DE JULIO -26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D14187-2546-48FA-AAFB-A8DF89569381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6C9748-DB30-4D39-9CEB-7E65D9CAC549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1215,27 +1215,6 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1275,8 +1254,26 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1286,6 +1283,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1309,10 +1309,74 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1335,18 +1399,10 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
@@ -1355,18 +1411,10 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
@@ -1375,58 +1423,10 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
@@ -1470,14 +1470,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla110" displayName="Tabla110" ref="C4:H103" totalsRowShown="0">
   <autoFilter ref="C4:H103" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" dataDxfId="25">
       <calculatedColumnFormula>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Producto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Cantidad"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Precio"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Descuento"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Importa" dataDxfId="22">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Importa" dataDxfId="24">
       <calculatedColumnFormula>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1489,14 +1489,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla111" displayName="Tabla111" ref="C4:H103" totalsRowShown="0">
   <autoFilter ref="C4:H103" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="#" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="#" dataDxfId="23">
       <calculatedColumnFormula>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Producto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Cantidad"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Precio"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Descuento"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Importa" dataDxfId="18">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Importa" dataDxfId="22">
       <calculatedColumnFormula>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1508,14 +1508,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla112" displayName="Tabla112" ref="C4:H103" totalsRowShown="0">
   <autoFilter ref="C4:H103" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="#" dataDxfId="21">
       <calculatedColumnFormula>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Producto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Cantidad"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Precio"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Descuento"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Importa" dataDxfId="14">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Importa" dataDxfId="20">
       <calculatedColumnFormula>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1527,14 +1527,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla113" displayName="Tabla113" ref="C4:H103" totalsRowShown="0">
   <autoFilter ref="C4:H103" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#" dataDxfId="19">
       <calculatedColumnFormula>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Producto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Cantidad"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Precio"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Descuento"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Importa" dataDxfId="10">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Importa" dataDxfId="18">
       <calculatedColumnFormula>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1546,14 +1546,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabla114" displayName="Tabla114" ref="C4:H103" totalsRowShown="0">
   <autoFilter ref="C4:H103" xr:uid="{00000000-0009-0000-0100-00000D000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="#" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="#" dataDxfId="17">
       <calculatedColumnFormula>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Producto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Cantidad"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Precio"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Descuento"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Importa" dataDxfId="6">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Importa" dataDxfId="16">
       <calculatedColumnFormula>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1565,14 +1565,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabla115" displayName="Tabla115" ref="C4:H103" totalsRowShown="0">
   <autoFilter ref="C4:H103" xr:uid="{00000000-0009-0000-0100-00000E000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="#" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="#" dataDxfId="15">
       <calculatedColumnFormula>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Producto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Cantidad"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Precio"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Descuento"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Importa" dataDxfId="2">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Importa" dataDxfId="14">
       <calculatedColumnFormula>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1874,23 +1874,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -1903,14 +1903,14 @@
         <f>SUM(Tabla1[Importa])</f>
         <v>2593.5</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -1941,19 +1941,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>26</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -1972,21 +1972,21 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>30</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C36" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -2005,19 +2005,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>24</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -2039,19 +2039,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>526</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -2073,19 +2073,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -2107,19 +2107,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>144</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -2138,19 +2138,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -2169,19 +2169,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -2203,19 +2203,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>297</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -2237,19 +2237,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>65</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -2268,19 +2268,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>60</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -2299,17 +2299,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>150</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -2328,17 +2328,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>48</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -2357,17 +2357,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>24</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -2386,17 +2386,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>40</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -2415,17 +2415,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>130</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -2444,17 +2444,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -2473,17 +2473,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -2505,17 +2505,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>157.5</v>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -2541,7 +2541,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -2563,19 +2563,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>18</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -2594,17 +2594,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -2623,23 +2623,23 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G26))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M26" s="38" t="s">
+      <c r="M26" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="38"/>
+      <c r="N26" s="31"/>
       <c r="O26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="P26" s="38" t="s">
+      <c r="P26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -2658,21 +2658,21 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G27))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>100</v>
       </c>
-      <c r="M27" s="26" t="s">
+      <c r="M27" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="N27" s="27"/>
-      <c r="O27" s="30">
+      <c r="N27" s="20"/>
+      <c r="O27" s="23">
         <v>4009</v>
       </c>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="34"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="27"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -2691,17 +2691,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G28))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>28</v>
       </c>
-      <c r="M28" s="28"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="36"/>
-      <c r="R28" s="37"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="30"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -2720,17 +2720,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G29))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>65</v>
       </c>
-      <c r="M29" s="26"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="34"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="27"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -2749,12 +2749,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G30))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>190</v>
       </c>
-      <c r="M30" s="28"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="31"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="36"/>
-      <c r="R30" s="37"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="30"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -2769,12 +2769,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G31))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M31" s="26"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="34"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="27"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -2789,12 +2789,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G32))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M32" s="28"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="37"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="30"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -2809,12 +2809,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G33))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M33" s="26"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="32"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="34"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="23"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="27"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -2829,12 +2829,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G34))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M34" s="28"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="37"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="30"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -2849,12 +2849,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G35))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M35" s="26"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="30"/>
-      <c r="P35" s="32"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="34"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="27"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -2869,12 +2869,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G36))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M36" s="28"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="36"/>
-      <c r="R36" s="37"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="30"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -2889,12 +2889,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G37))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M37" s="26"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="32"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="34"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="27"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -2909,12 +2909,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G38))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M38" s="28"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="36"/>
-      <c r="R38" s="37"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="30"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -2929,12 +2929,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G39))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M39" s="26"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="30"/>
-      <c r="P39" s="32"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="34"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="27"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -2949,12 +2949,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G40))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M40" s="28"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="36"/>
-      <c r="R40" s="37"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="30"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -2969,12 +2969,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G41))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M41" s="26"/>
-      <c r="N41" s="27"/>
-      <c r="O41" s="30"/>
-      <c r="P41" s="32"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="34"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="25"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="27"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -2989,12 +2989,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G42))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M42" s="28"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="35"/>
-      <c r="Q42" s="36"/>
-      <c r="R42" s="37"/>
+      <c r="M42" s="21"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="30"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -3009,12 +3009,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G43))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M43" s="26"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="34"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="23"/>
+      <c r="P43" s="25"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="27"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -3029,12 +3029,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G44))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M44" s="28"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="31"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="36"/>
-      <c r="R44" s="37"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="29"/>
+      <c r="R44" s="30"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -3049,12 +3049,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G45))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M45" s="26"/>
-      <c r="N45" s="27"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="32"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="34"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="23"/>
+      <c r="P45" s="25"/>
+      <c r="Q45" s="26"/>
+      <c r="R45" s="27"/>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="18" t="str">
@@ -3069,12 +3069,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G46))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M46" s="28"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="36"/>
-      <c r="R46" s="37"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="30"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="18" t="str">
@@ -3089,12 +3089,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G47))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M47" s="26"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="32"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="34"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="23"/>
+      <c r="P47" s="25"/>
+      <c r="Q47" s="26"/>
+      <c r="R47" s="27"/>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="str">
@@ -3109,12 +3109,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G48))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M48" s="28"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="35"/>
-      <c r="Q48" s="36"/>
-      <c r="R48" s="37"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="30"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" s="18" t="str">
@@ -3129,12 +3129,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G49))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M49" s="26"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="32"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="34"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="23"/>
+      <c r="P49" s="25"/>
+      <c r="Q49" s="26"/>
+      <c r="R49" s="27"/>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="18" t="str">
@@ -3149,12 +3149,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G50))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M50" s="28"/>
-      <c r="N50" s="29"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="35"/>
-      <c r="Q50" s="36"/>
-      <c r="R50" s="37"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="24"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="29"/>
+      <c r="R50" s="30"/>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="18" t="str">
@@ -3169,12 +3169,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G51))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M51" s="26"/>
-      <c r="N51" s="27"/>
-      <c r="O51" s="30"/>
-      <c r="P51" s="32"/>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="34"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="20"/>
+      <c r="O51" s="23"/>
+      <c r="P51" s="25"/>
+      <c r="Q51" s="26"/>
+      <c r="R51" s="27"/>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B52" s="18" t="str">
@@ -3189,12 +3189,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G52))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M52" s="28"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="31"/>
-      <c r="P52" s="35"/>
-      <c r="Q52" s="36"/>
-      <c r="R52" s="37"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="22"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="30"/>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="18" t="str">
@@ -3913,33 +3913,19 @@
   </sheetData>
   <autoFilter ref="B4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="48">
-    <mergeCell ref="M49:N50"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P49:R50"/>
-    <mergeCell ref="M51:N52"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="P51:R52"/>
-    <mergeCell ref="M45:N46"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="P45:R46"/>
-    <mergeCell ref="M47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:R48"/>
-    <mergeCell ref="P31:R32"/>
-    <mergeCell ref="P33:R34"/>
-    <mergeCell ref="P35:R36"/>
-    <mergeCell ref="P37:R38"/>
-    <mergeCell ref="P39:R40"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="O33:O34"/>
-    <mergeCell ref="O35:O36"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="M31:N32"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="M35:N36"/>
-    <mergeCell ref="M37:N38"/>
-    <mergeCell ref="M39:N40"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M41:N42"/>
+    <mergeCell ref="M43:N44"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="P41:R42"/>
+    <mergeCell ref="P43:R44"/>
     <mergeCell ref="P26:R26"/>
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="M27:N28"/>
@@ -3948,27 +3934,41 @@
     <mergeCell ref="O29:O30"/>
     <mergeCell ref="P27:R28"/>
     <mergeCell ref="P29:R30"/>
-    <mergeCell ref="M41:N42"/>
-    <mergeCell ref="M43:N44"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="P41:R42"/>
-    <mergeCell ref="P43:R44"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M31:N32"/>
+    <mergeCell ref="M33:N34"/>
+    <mergeCell ref="M35:N36"/>
+    <mergeCell ref="M37:N38"/>
+    <mergeCell ref="M39:N40"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="P31:R32"/>
+    <mergeCell ref="P33:R34"/>
+    <mergeCell ref="P35:R36"/>
+    <mergeCell ref="P37:R38"/>
+    <mergeCell ref="P39:R40"/>
+    <mergeCell ref="M45:N46"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="P45:R46"/>
+    <mergeCell ref="M47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:R48"/>
+    <mergeCell ref="M49:N50"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P49:R50"/>
+    <mergeCell ref="M51:N52"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="P51:R52"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>C5&gt;0&amp;ISBLANK(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D6">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>E5&gt;0&amp;ISBLANK(D5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4000,23 +4000,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -4029,14 +4029,14 @@
         <f>SUM(Tabla110[Importa])</f>
         <v>2592</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -4067,19 +4067,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>24</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla110[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -4101,21 +4101,21 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>68.5</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -4137,19 +4137,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>72</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -4168,19 +4168,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>60</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -4202,19 +4202,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>72</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -4236,19 +4236,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>18</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -4270,19 +4270,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>25.5</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -4301,19 +4301,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>164</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -4332,19 +4332,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>100</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -4363,19 +4363,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>65</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -4397,19 +4397,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>76.5</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -4428,17 +4428,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -4457,17 +4457,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -4486,17 +4486,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>840</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -4515,17 +4515,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>99</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -4547,17 +4547,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -4576,17 +4576,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>6</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -4605,17 +4605,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -4634,17 +4634,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>150</v>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -4667,7 +4667,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -4686,19 +4686,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>170</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -4717,17 +4717,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>230</v>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -4752,17 +4752,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -4787,15 +4787,15 @@
       <c r="N27" s="15">
         <v>3591</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -4819,15 +4819,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -4839,15 +4839,15 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -4859,10 +4859,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -4879,10 +4879,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -4899,10 +4899,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -4919,10 +4919,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -4939,10 +4939,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -4959,10 +4959,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -4979,10 +4979,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -4999,10 +4999,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -5019,10 +5019,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -5039,10 +5039,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -5059,10 +5059,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -5079,10 +5079,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -5099,10 +5099,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -5119,10 +5119,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -5139,10 +5139,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -5972,40 +5972,40 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>C5&gt;0&amp;ISBLANK(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D6">
-    <cfRule type="expression" dxfId="24" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>E5&gt;0&amp;ISBLANK(D5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6036,23 +6036,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -6065,14 +6065,14 @@
         <f>SUM(Tabla111[Importa])</f>
         <v>3652.5</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -6103,19 +6103,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>20</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla111[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -6134,21 +6134,21 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -6167,19 +6167,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>100</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C7">
         <f>IF(ISNUMBER(E7), IF(ISNUMBER(C6), C6+1, 1), "")</f>
@@ -6198,19 +6198,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>140</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C68" si="1">IF(ISNUMBER(E8), IF(ISNUMBER(C7), C7+1, 1), "")</f>
@@ -6232,19 +6232,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>36</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
@@ -6266,19 +6266,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>630</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -6297,19 +6297,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>160</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -6331,19 +6331,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -6362,19 +6362,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -6393,19 +6393,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>1500</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -6424,19 +6424,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>175</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C15">
         <f t="shared" si="1"/>
@@ -6455,17 +6455,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>130</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C16">
         <f t="shared" si="1"/>
@@ -6484,17 +6484,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C17">
         <f t="shared" si="1"/>
@@ -6513,17 +6513,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>130</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C18">
         <f t="shared" si="1"/>
@@ -6542,17 +6542,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C19">
         <f t="shared" si="1"/>
@@ -6571,17 +6571,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C20">
         <f t="shared" si="1"/>
@@ -6600,17 +6600,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C21">
         <f t="shared" si="1"/>
@@ -6632,17 +6632,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>101</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C22">
         <f t="shared" si="1"/>
@@ -6661,17 +6661,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C23">
         <f t="shared" si="1"/>
@@ -6697,7 +6697,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C24">
         <f t="shared" si="1"/>
@@ -6716,19 +6716,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>175</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="1"/>
@@ -6738,17 +6738,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="1"/>
@@ -6764,17 +6764,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="1"/>
@@ -6790,15 +6790,15 @@
       <c r="N27" s="15">
         <v>2670</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="1"/>
@@ -6810,15 +6810,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="1"/>
@@ -6830,15 +6830,15 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="1"/>
@@ -6850,10 +6850,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -6870,10 +6870,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -6890,10 +6890,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -6910,10 +6910,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -6930,10 +6930,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -6950,10 +6950,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -6970,10 +6970,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -6990,10 +6990,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -7010,10 +7010,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -7030,10 +7030,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -7050,10 +7050,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -7070,10 +7070,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -7090,10 +7090,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -7110,10 +7110,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -7130,10 +7130,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -7963,40 +7963,40 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>C5&gt;0&amp;ISBLANK(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D6">
-    <cfRule type="expression" dxfId="20" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>E5&gt;0&amp;ISBLANK(D5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8026,23 +8026,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -8055,14 +8055,14 @@
         <f>SUM(Tabla112[Importa])</f>
         <v>2701.5</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -8093,17 +8093,17 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>14</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla112[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -8122,21 +8122,21 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>147</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -8155,19 +8155,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>35</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -8189,19 +8189,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>54</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -8223,19 +8223,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -8257,19 +8257,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -8291,19 +8291,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>153</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -8325,19 +8325,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>34.5</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -8356,19 +8356,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>6</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -8390,19 +8390,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>450</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -8424,19 +8424,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>40.5</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -8458,17 +8458,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>58.5</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -8487,17 +8487,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>980</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -8516,17 +8516,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>500</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -8548,17 +8548,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>63</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -8568,17 +8568,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -8588,17 +8588,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -8608,17 +8608,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -8628,17 +8628,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -8652,7 +8652,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -8662,19 +8662,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -8684,17 +8684,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -8710,17 +8710,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -8732,15 +8732,15 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -8752,15 +8752,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -8772,15 +8772,15 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -8792,10 +8792,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -8812,10 +8812,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -8832,10 +8832,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -8852,10 +8852,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -8872,10 +8872,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -8892,10 +8892,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -8912,10 +8912,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -8932,10 +8932,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -8952,10 +8952,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -8972,10 +8972,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -8992,10 +8992,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -9012,10 +9012,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -9032,10 +9032,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -9052,10 +9052,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -9072,10 +9072,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -9905,40 +9905,40 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>C5&gt;0&amp;ISBLANK(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D6">
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>E5&gt;0&amp;ISBLANK(D5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9969,23 +9969,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -9998,14 +9998,14 @@
         <f>SUM(Tabla113[Importa])</f>
         <v>1590.5</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -10036,19 +10036,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>13</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla113[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -10067,21 +10067,21 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -10100,19 +10100,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>60</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -10131,19 +10131,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>32</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -10162,19 +10162,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>95</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -10193,19 +10193,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -10224,19 +10224,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>280</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -10255,19 +10255,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -10286,19 +10286,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>65</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -10320,19 +10320,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>495</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -10354,19 +10354,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>108</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -10388,17 +10388,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>18</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -10420,17 +10420,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>63</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -10452,17 +10452,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>319.5</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -10472,17 +10472,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -10492,17 +10492,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -10512,17 +10512,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -10532,17 +10532,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -10552,17 +10552,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -10576,7 +10576,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -10586,19 +10586,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -10608,17 +10608,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -10634,17 +10634,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -10660,17 +10660,17 @@
       <c r="N27" s="15">
         <v>4009</v>
       </c>
-      <c r="O27" s="40" t="s">
+      <c r="O27" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -10686,17 +10686,17 @@
       <c r="N28" s="15">
         <v>3591</v>
       </c>
-      <c r="O28" s="40" t="s">
+      <c r="O28" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -10712,17 +10712,17 @@
       <c r="N29" s="15">
         <v>2670</v>
       </c>
-      <c r="O29" s="40" t="s">
+      <c r="O29" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -10738,12 +10738,12 @@
       <c r="N30" s="15">
         <v>1500</v>
       </c>
-      <c r="O30" s="40" t="s">
+      <c r="O30" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -10764,12 +10764,12 @@
       <c r="N31" s="15">
         <v>11770</v>
       </c>
-      <c r="O31" s="40" t="s">
+      <c r="O31" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -10786,10 +10786,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -10806,10 +10806,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -10826,10 +10826,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -10846,10 +10846,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -10866,10 +10866,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -10886,10 +10886,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -10906,10 +10906,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -10926,10 +10926,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -10946,10 +10946,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -10966,10 +10966,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -10986,10 +10986,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -11006,10 +11006,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -11026,10 +11026,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -11859,40 +11859,40 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>C5&gt;0&amp;ISBLANK(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D6">
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>E5&gt;0&amp;ISBLANK(D5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11922,23 +11922,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -11951,14 +11951,14 @@
         <f>SUM(Tabla114[Importa])</f>
         <v>3302.5</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -11989,19 +11989,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>36</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla114[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -12023,21 +12023,21 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -12059,19 +12059,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>71.5</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -12093,19 +12093,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>78.5</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -12127,19 +12127,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>96.5</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -12161,19 +12161,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>72</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -12195,19 +12195,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>58.5</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -12229,19 +12229,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>153</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -12260,19 +12260,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -12291,19 +12291,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>3</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -12325,19 +12325,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>153</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -12356,17 +12356,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>75</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -12385,17 +12385,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>65</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -12414,17 +12414,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>65</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -12446,17 +12446,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>261</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -12478,17 +12478,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -12510,17 +12510,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>76.5</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -12542,17 +12542,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -12574,17 +12574,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -12610,7 +12610,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -12632,19 +12632,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>123.5</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -12666,17 +12666,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>36</v>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -12701,17 +12701,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -12732,15 +12732,15 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -12764,15 +12764,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -12793,15 +12793,15 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -12822,10 +12822,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -12851,10 +12851,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -12880,10 +12880,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -12909,10 +12909,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -12938,10 +12938,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -12967,10 +12967,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -12996,10 +12996,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -13025,10 +13025,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -13054,10 +13054,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -13083,10 +13083,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -13112,10 +13112,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -13132,10 +13132,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -13152,10 +13152,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -13172,10 +13172,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -13192,10 +13192,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -14025,40 +14025,40 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>C5&gt;0&amp;ISBLANK(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D6">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>E5&gt;0&amp;ISBLANK(D5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14088,23 +14088,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -14117,14 +14117,14 @@
         <f>SUM(Tabla115[Importa])</f>
         <v>0</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -14155,12 +14155,12 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="str">
@@ -14175,21 +14175,21 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -14199,19 +14199,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -14221,19 +14221,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -14243,19 +14243,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -14265,19 +14265,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -14287,19 +14287,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -14309,19 +14309,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -14331,19 +14331,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -14353,19 +14353,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -14375,19 +14375,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -14397,17 +14397,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -14417,17 +14417,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -14437,17 +14437,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -14457,17 +14457,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -14477,17 +14477,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -14497,17 +14497,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -14517,17 +14517,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -14537,17 +14537,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -14561,7 +14561,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -14571,19 +14571,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -14593,17 +14593,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -14619,17 +14619,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -14641,15 +14641,15 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -14661,15 +14661,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -14681,15 +14681,15 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46207.793529976851</v>
+        <v>46209.717254976851</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -14701,10 +14701,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -14721,10 +14721,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -14741,10 +14741,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -14761,10 +14761,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -14781,10 +14781,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -14801,10 +14801,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -14821,10 +14821,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -14841,10 +14841,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -14861,10 +14861,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -14881,10 +14881,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -14901,10 +14901,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -14921,10 +14921,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -14941,10 +14941,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -14961,10 +14961,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -14981,10 +14981,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -15814,40 +15814,40 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>C5&gt;0&amp;ISBLANK(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D6">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>E5&gt;0&amp;ISBLANK(D5)</formula>
     </cfRule>
   </conditionalFormatting>
